--- a/AAII_Financials/Quarterly/DELHY_QTR_FIN.xlsx
+++ b/AAII_Financials/Quarterly/DELHY_QTR_FIN.xlsx
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="389" uniqueCount="92">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="431" uniqueCount="92">
   <si>
     <t>DELHY</t>
   </si>
@@ -656,78 +656,84 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet2"/>
-  <dimension ref="A5:Q102"/>
+  <dimension ref="A5:S102"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="9" style="1" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="26.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="69.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="11" width="15.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="12" max="13" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="14" max="14" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="15" max="15" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="16" max="17" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="18" max="16384" width="9.140625" style="1"/>
+    <col min="4" max="13" width="15.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="14" max="15" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="16" max="16" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="17" max="17" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="18" max="19" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="20" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
-    <row r="5" spans="1:17" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A5" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:17" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:19" x14ac:dyDescent="0.2">
       <c r="B6" s="1" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:17" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:19" x14ac:dyDescent="0.2">
       <c r="C7" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D7" s="2">
+        <v>46203</v>
+      </c>
+      <c r="E7" s="2">
+        <v>46112</v>
+      </c>
+      <c r="F7" s="2">
         <v>46022</v>
       </c>
-      <c r="E7" s="2">
+      <c r="G7" s="2">
         <v>45930</v>
       </c>
-      <c r="F7" s="2">
+      <c r="H7" s="2">
         <v>45838</v>
       </c>
-      <c r="G7" s="2">
+      <c r="I7" s="2">
         <v>45747</v>
       </c>
-      <c r="H7" s="2">
+      <c r="J7" s="2">
         <v>45657</v>
       </c>
-      <c r="I7" s="2">
+      <c r="K7" s="2">
         <v>45565</v>
       </c>
-      <c r="J7" s="2">
+      <c r="L7" s="2">
         <v>45473</v>
       </c>
-      <c r="K7" s="2">
+      <c r="M7" s="2">
         <v>45382</v>
       </c>
-      <c r="L7" s="2">
+      <c r="N7" s="2">
         <v>45291</v>
       </c>
-      <c r="M7" s="2">
+      <c r="O7" s="2">
         <v>45199</v>
       </c>
-      <c r="N7" s="2">
+      <c r="P7" s="2">
         <v>45107</v>
       </c>
-      <c r="O7" s="2">
+      <c r="Q7" s="2">
         <v>45016</v>
       </c>
-      <c r="P7" s="2">
+      <c r="R7" s="2">
         <v>44926</v>
       </c>
-      <c r="Q7" s="2">
+      <c r="S7" s="2">
         <v>44834</v>
       </c>
     </row>
-    <row r="8" spans="1:17" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:19" x14ac:dyDescent="0.2">
       <c r="C8" s="1" t="s">
         <v>3</v>
       </c>
@@ -773,8 +779,14 @@
       <c r="Q8" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="9" spans="1:17" x14ac:dyDescent="0.2">
+      <c r="R8" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="S8" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="9" spans="1:19" x14ac:dyDescent="0.2">
       <c r="C9" s="1" t="s">
         <v>5</v>
       </c>
@@ -820,8 +832,14 @@
       <c r="Q9" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="10" spans="1:17" x14ac:dyDescent="0.2">
+      <c r="R9" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="S9" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="10" spans="1:19" x14ac:dyDescent="0.2">
       <c r="C10" s="1" t="s">
         <v>6</v>
       </c>
@@ -867,8 +885,14 @@
       <c r="Q10" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="11" spans="1:17" x14ac:dyDescent="0.2">
+      <c r="R10" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="S10" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="11" spans="1:19" x14ac:dyDescent="0.2">
       <c r="C11" s="1" t="s">
         <v>7</v>
       </c>
@@ -886,8 +910,10 @@
       <c r="O11" s="3"/>
       <c r="P11" s="3"/>
       <c r="Q11" s="3"/>
-    </row>
-    <row r="12" spans="1:17" x14ac:dyDescent="0.2">
+      <c r="R11" s="3"/>
+      <c r="S11" s="3"/>
+    </row>
+    <row r="12" spans="1:19" x14ac:dyDescent="0.2">
       <c r="C12" s="1" t="s">
         <v>8</v>
       </c>
@@ -933,8 +959,14 @@
       <c r="Q12" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="13" spans="1:17" x14ac:dyDescent="0.2">
+      <c r="R12" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="S12" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="13" spans="1:19" x14ac:dyDescent="0.2">
       <c r="C13" s="1" t="s">
         <v>9</v>
       </c>
@@ -980,8 +1012,14 @@
       <c r="Q13" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="14" spans="1:17" x14ac:dyDescent="0.2">
+      <c r="R13" s="3">
+        <v>0</v>
+      </c>
+      <c r="S13" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="14" spans="1:19" x14ac:dyDescent="0.2">
       <c r="C14" s="1" t="s">
         <v>10</v>
       </c>
@@ -1027,8 +1065,14 @@
       <c r="Q14" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="15" spans="1:17" x14ac:dyDescent="0.2">
+      <c r="R14" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="S14" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="15" spans="1:19" x14ac:dyDescent="0.2">
       <c r="C15" s="1" t="s">
         <v>11</v>
       </c>
@@ -1074,8 +1118,14 @@
       <c r="Q15" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="16" spans="1:17" x14ac:dyDescent="0.2">
+      <c r="R15" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="S15" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="16" spans="1:19" x14ac:dyDescent="0.2">
       <c r="D16" s="3"/>
       <c r="E16" s="3"/>
       <c r="F16" s="3"/>
@@ -1090,8 +1140,10 @@
       <c r="O16" s="3"/>
       <c r="P16" s="3"/>
       <c r="Q16" s="3"/>
-    </row>
-    <row r="17" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R16" s="3"/>
+      <c r="S16" s="3"/>
+    </row>
+    <row r="17" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C17" s="1" t="s">
         <v>12</v>
       </c>
@@ -1137,8 +1189,14 @@
       <c r="Q17" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="18" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R17" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="S17" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="18" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C18" s="1" t="s">
         <v>13</v>
       </c>
@@ -1184,8 +1242,14 @@
       <c r="Q18" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="19" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R18" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="S18" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="19" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C19" s="1" t="s">
         <v>14</v>
       </c>
@@ -1203,8 +1267,10 @@
       <c r="O19" s="3"/>
       <c r="P19" s="3"/>
       <c r="Q19" s="3"/>
-    </row>
-    <row r="20" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R19" s="3"/>
+      <c r="S19" s="3"/>
+    </row>
+    <row r="20" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C20" s="1" t="s">
         <v>15</v>
       </c>
@@ -1250,8 +1316,14 @@
       <c r="Q20" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="21" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R20" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="S20" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="21" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C21" s="1" t="s">
         <v>16</v>
       </c>
@@ -1297,8 +1369,14 @@
       <c r="Q21" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="22" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R21" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="S21" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="22" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C22" s="1" t="s">
         <v>17</v>
       </c>
@@ -1344,8 +1422,14 @@
       <c r="Q22" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="23" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R22" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="S22" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="23" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C23" s="1" t="s">
         <v>18</v>
       </c>
@@ -1391,8 +1475,14 @@
       <c r="Q23" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="24" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R23" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="S23" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="24" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C24" s="1" t="s">
         <v>19</v>
       </c>
@@ -1438,8 +1528,14 @@
       <c r="Q24" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="25" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R24" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="S24" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="25" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C25" s="1" t="s">
         <v>20</v>
       </c>
@@ -1485,8 +1581,14 @@
       <c r="Q25" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="26" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R25" s="3">
+        <v>0</v>
+      </c>
+      <c r="S25" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="26" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C26" s="1" t="s">
         <v>21</v>
       </c>
@@ -1532,8 +1634,14 @@
       <c r="Q26" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="27" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R26" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="S26" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="27" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C27" s="1" t="s">
         <v>22</v>
       </c>
@@ -1579,8 +1687,14 @@
       <c r="Q27" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="28" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R27" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="S27" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="28" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C28" s="1" t="s">
         <v>23</v>
       </c>
@@ -1626,8 +1740,14 @@
       <c r="Q28" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="29" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R28" s="3">
+        <v>0</v>
+      </c>
+      <c r="S28" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="29" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C29" s="1" t="s">
         <v>24</v>
       </c>
@@ -1673,8 +1793,14 @@
       <c r="Q29" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="30" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R29" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="S29" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="30" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C30" s="1" t="s">
         <v>25</v>
       </c>
@@ -1720,8 +1846,14 @@
       <c r="Q30" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="31" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R30" s="3">
+        <v>0</v>
+      </c>
+      <c r="S30" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="31" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C31" s="1" t="s">
         <v>26</v>
       </c>
@@ -1767,8 +1899,14 @@
       <c r="Q31" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="32" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R31" s="3">
+        <v>0</v>
+      </c>
+      <c r="S31" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="32" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C32" s="1" t="s">
         <v>27</v>
       </c>
@@ -1814,8 +1952,14 @@
       <c r="Q32" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="33" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="R32" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="S32" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="33" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C33" s="1" t="s">
         <v>28</v>
       </c>
@@ -1861,8 +2005,14 @@
       <c r="Q33" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="34" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="R33" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="S33" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="34" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C34" s="1" t="s">
         <v>29</v>
       </c>
@@ -1908,8 +2058,14 @@
       <c r="Q34" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="35" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="R34" s="3">
+        <v>0</v>
+      </c>
+      <c r="S34" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="35" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C35" s="1" t="s">
         <v>30</v>
       </c>
@@ -1955,60 +2111,72 @@
       <c r="Q35" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="37" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="R35" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="S35" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="37" spans="2:19" x14ac:dyDescent="0.2">
       <c r="B37" s="1" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="38" spans="2:17" x14ac:dyDescent="0.2">
+    <row r="38" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C38" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D38" s="2">
+        <v>46203</v>
+      </c>
+      <c r="E38" s="2">
+        <v>46112</v>
+      </c>
+      <c r="F38" s="2">
         <v>46022</v>
       </c>
-      <c r="E38" s="2">
+      <c r="G38" s="2">
         <v>45930</v>
       </c>
-      <c r="F38" s="2">
+      <c r="H38" s="2">
         <v>45838</v>
       </c>
-      <c r="G38" s="2">
+      <c r="I38" s="2">
         <v>45747</v>
       </c>
-      <c r="H38" s="2">
+      <c r="J38" s="2">
         <v>45657</v>
       </c>
-      <c r="I38" s="2">
+      <c r="K38" s="2">
         <v>45565</v>
       </c>
-      <c r="J38" s="2">
+      <c r="L38" s="2">
         <v>45473</v>
       </c>
-      <c r="K38" s="2">
+      <c r="M38" s="2">
         <v>45382</v>
       </c>
-      <c r="L38" s="2">
+      <c r="N38" s="2">
         <v>45291</v>
       </c>
-      <c r="M38" s="2">
+      <c r="O38" s="2">
         <v>45199</v>
       </c>
-      <c r="N38" s="2">
+      <c r="P38" s="2">
         <v>45107</v>
       </c>
-      <c r="O38" s="2">
+      <c r="Q38" s="2">
         <v>45016</v>
       </c>
-      <c r="P38" s="2">
+      <c r="R38" s="2">
         <v>44926</v>
       </c>
-      <c r="Q38" s="2">
+      <c r="S38" s="2">
         <v>44834</v>
       </c>
     </row>
-    <row r="39" spans="2:17" x14ac:dyDescent="0.2">
+    <row r="39" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C39" s="1" t="s">
         <v>32</v>
       </c>
@@ -2026,8 +2194,10 @@
       <c r="O39" s="3"/>
       <c r="P39" s="3"/>
       <c r="Q39" s="3"/>
-    </row>
-    <row r="40" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="R39" s="3"/>
+      <c r="S39" s="3"/>
+    </row>
+    <row r="40" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C40" s="1" t="s">
         <v>33</v>
       </c>
@@ -2045,55 +2215,63 @@
       <c r="O40" s="3"/>
       <c r="P40" s="3"/>
       <c r="Q40" s="3"/>
-    </row>
-    <row r="41" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="R40" s="3"/>
+      <c r="S40" s="3"/>
+    </row>
+    <row r="41" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C41" s="1" t="s">
         <v>34</v>
       </c>
       <c r="D41" s="3">
+        <v>3081500</v>
+      </c>
+      <c r="E41" s="3">
+        <v>3109900</v>
+      </c>
+      <c r="F41" s="3">
         <v>2480600</v>
       </c>
-      <c r="E41" s="3">
+      <c r="G41" s="3">
         <v>2478800</v>
       </c>
-      <c r="F41" s="3">
+      <c r="H41" s="3">
         <v>3297800</v>
       </c>
-      <c r="G41" s="3">
+      <c r="I41" s="3">
         <v>3035100</v>
       </c>
-      <c r="H41" s="3">
+      <c r="J41" s="3">
         <v>3943200</v>
       </c>
-      <c r="I41" s="3">
+      <c r="K41" s="3">
         <v>4247900</v>
       </c>
-      <c r="J41" s="3">
+      <c r="L41" s="3">
         <v>1881400</v>
       </c>
-      <c r="K41" s="3">
+      <c r="M41" s="3">
         <v>1894400</v>
       </c>
-      <c r="L41" s="3">
+      <c r="N41" s="3">
         <v>1834200</v>
       </c>
-      <c r="M41" s="3">
+      <c r="O41" s="3">
         <v>1756400</v>
       </c>
-      <c r="N41" s="3">
+      <c r="P41" s="3">
         <v>2100500</v>
       </c>
-      <c r="O41" s="3">
+      <c r="Q41" s="3">
         <v>2090500</v>
       </c>
-      <c r="P41" s="3">
+      <c r="R41" s="3">
         <v>2583900</v>
       </c>
-      <c r="Q41" s="3">
+      <c r="S41" s="3">
         <v>2370900</v>
       </c>
     </row>
-    <row r="42" spans="2:17" x14ac:dyDescent="0.2">
+    <row r="42" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C42" s="1" t="s">
         <v>35</v>
       </c>
@@ -2139,337 +2317,385 @@
       <c r="Q42" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="43" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="R42" s="3">
+        <v>0</v>
+      </c>
+      <c r="S42" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="43" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C43" s="1" t="s">
         <v>36</v>
       </c>
       <c r="D43" s="3">
+        <v>776000</v>
+      </c>
+      <c r="E43" s="3">
+        <v>783100</v>
+      </c>
+      <c r="F43" s="3">
         <v>745600</v>
       </c>
-      <c r="E43" s="3">
+      <c r="G43" s="3">
         <v>745000</v>
       </c>
-      <c r="F43" s="3">
+      <c r="H43" s="3">
         <v>921300</v>
       </c>
-      <c r="G43" s="3">
+      <c r="I43" s="3">
         <v>847900</v>
       </c>
-      <c r="H43" s="3">
+      <c r="J43" s="3">
         <v>682900</v>
       </c>
-      <c r="I43" s="3">
+      <c r="K43" s="3">
         <v>735700</v>
       </c>
-      <c r="J43" s="3">
+      <c r="L43" s="3">
         <v>877700</v>
       </c>
-      <c r="K43" s="3">
+      <c r="M43" s="3">
         <v>883800</v>
       </c>
-      <c r="L43" s="3">
+      <c r="N43" s="3">
         <v>769800</v>
       </c>
-      <c r="M43" s="3">
+      <c r="O43" s="3">
         <v>737100</v>
       </c>
-      <c r="N43" s="3">
+      <c r="P43" s="3">
         <v>644300</v>
       </c>
-      <c r="O43" s="3">
+      <c r="Q43" s="3">
         <v>641200</v>
       </c>
-      <c r="P43" s="3">
+      <c r="R43" s="3">
         <v>645800</v>
       </c>
-      <c r="Q43" s="3">
+      <c r="S43" s="3">
         <v>592600</v>
       </c>
     </row>
-    <row r="44" spans="2:17" x14ac:dyDescent="0.2">
+    <row r="44" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C44" s="1" t="s">
         <v>37</v>
       </c>
       <c r="D44" s="3">
+        <v>264100</v>
+      </c>
+      <c r="E44" s="3">
+        <v>266600</v>
+      </c>
+      <c r="F44" s="3">
         <v>223800</v>
       </c>
-      <c r="E44" s="3">
+      <c r="G44" s="3">
         <v>223600</v>
       </c>
-      <c r="F44" s="3">
+      <c r="H44" s="3">
         <v>213900</v>
       </c>
-      <c r="G44" s="3">
+      <c r="I44" s="3">
         <v>196800</v>
       </c>
-      <c r="H44" s="3">
+      <c r="J44" s="3">
         <v>180800</v>
       </c>
-      <c r="I44" s="3">
+      <c r="K44" s="3">
         <v>194700</v>
       </c>
-      <c r="J44" s="3">
+      <c r="L44" s="3">
         <v>168100</v>
       </c>
-      <c r="K44" s="3">
+      <c r="M44" s="3">
         <v>169300</v>
       </c>
-      <c r="L44" s="3">
+      <c r="N44" s="3">
         <v>158600</v>
       </c>
-      <c r="M44" s="3">
+      <c r="O44" s="3">
         <v>151900</v>
       </c>
-      <c r="N44" s="3">
+      <c r="P44" s="3">
         <v>162800</v>
       </c>
-      <c r="O44" s="3">
+      <c r="Q44" s="3">
         <v>162000</v>
       </c>
-      <c r="P44" s="3">
+      <c r="R44" s="3">
         <v>151000</v>
       </c>
-      <c r="Q44" s="3">
+      <c r="S44" s="3">
         <v>138600</v>
       </c>
     </row>
-    <row r="45" spans="2:17" x14ac:dyDescent="0.2">
+    <row r="45" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C45" s="1" t="s">
         <v>38</v>
       </c>
       <c r="D45" s="3">
+        <v>521200</v>
+      </c>
+      <c r="E45" s="3">
+        <v>526000</v>
+      </c>
+      <c r="F45" s="3">
         <v>416100</v>
       </c>
-      <c r="E45" s="3">
+      <c r="G45" s="3">
         <v>415800</v>
       </c>
-      <c r="F45" s="3">
+      <c r="H45" s="3">
         <v>407000</v>
       </c>
-      <c r="G45" s="3">
+      <c r="I45" s="3">
         <v>374600</v>
       </c>
-      <c r="H45" s="3">
+      <c r="J45" s="3">
         <v>572900</v>
       </c>
-      <c r="I45" s="3">
+      <c r="K45" s="3">
         <v>617200</v>
       </c>
-      <c r="J45" s="3">
+      <c r="L45" s="3">
         <v>345000</v>
       </c>
-      <c r="K45" s="3">
+      <c r="M45" s="3">
         <v>347400</v>
       </c>
-      <c r="L45" s="3">
+      <c r="N45" s="3">
         <v>370500</v>
       </c>
-      <c r="M45" s="3">
+      <c r="O45" s="3">
         <v>354800</v>
       </c>
-      <c r="N45" s="3">
+      <c r="P45" s="3">
         <v>353200</v>
       </c>
-      <c r="O45" s="3">
+      <c r="Q45" s="3">
         <v>351500</v>
       </c>
-      <c r="P45" s="3">
+      <c r="R45" s="3">
         <v>390500</v>
       </c>
-      <c r="Q45" s="3">
+      <c r="S45" s="3">
         <v>358300</v>
       </c>
     </row>
-    <row r="46" spans="2:17" x14ac:dyDescent="0.2">
+    <row r="46" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C46" s="1" t="s">
         <v>39</v>
       </c>
       <c r="D46" s="3">
+        <v>4642800</v>
+      </c>
+      <c r="E46" s="3">
+        <v>4685600</v>
+      </c>
+      <c r="F46" s="3">
         <v>3866000</v>
       </c>
-      <c r="E46" s="3">
+      <c r="G46" s="3">
         <v>3863300</v>
       </c>
-      <c r="F46" s="3">
+      <c r="H46" s="3">
         <v>4840000</v>
       </c>
-      <c r="G46" s="3">
+      <c r="I46" s="3">
         <v>4454500</v>
       </c>
-      <c r="H46" s="3">
+      <c r="J46" s="3">
         <v>5379700</v>
       </c>
-      <c r="I46" s="3">
+      <c r="K46" s="3">
         <v>5795600</v>
       </c>
-      <c r="J46" s="3">
+      <c r="L46" s="3">
         <v>3272300</v>
       </c>
-      <c r="K46" s="3">
+      <c r="M46" s="3">
         <v>3294900</v>
       </c>
-      <c r="L46" s="3">
+      <c r="N46" s="3">
         <v>3133100</v>
       </c>
-      <c r="M46" s="3">
+      <c r="O46" s="3">
         <v>3000100</v>
       </c>
-      <c r="N46" s="3">
+      <c r="P46" s="3">
         <v>3260800</v>
       </c>
-      <c r="O46" s="3">
+      <c r="Q46" s="3">
         <v>3245200</v>
       </c>
-      <c r="P46" s="3">
+      <c r="R46" s="3">
         <v>3771300</v>
       </c>
-      <c r="Q46" s="3">
+      <c r="S46" s="3">
         <v>3460300</v>
       </c>
     </row>
-    <row r="47" spans="2:17" x14ac:dyDescent="0.2">
+    <row r="47" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C47" s="1" t="s">
         <v>40</v>
       </c>
       <c r="D47" s="3">
+        <v>100</v>
+      </c>
+      <c r="E47" s="3">
+        <v>100</v>
+      </c>
+      <c r="F47" s="3">
         <v>257700</v>
       </c>
-      <c r="E47" s="3">
+      <c r="G47" s="3">
         <v>257500</v>
       </c>
-      <c r="F47" s="3">
+      <c r="H47" s="3">
         <v>14700</v>
       </c>
-      <c r="G47" s="3">
+      <c r="I47" s="3">
         <v>13500</v>
       </c>
-      <c r="H47" s="3">
+      <c r="J47" s="3">
         <v>270000</v>
       </c>
-      <c r="I47" s="3">
+      <c r="K47" s="3">
         <v>290900</v>
       </c>
-      <c r="J47" s="3">
+      <c r="L47" s="3">
         <v>275000</v>
       </c>
-      <c r="K47" s="3">
+      <c r="M47" s="3">
         <v>276900</v>
       </c>
-      <c r="L47" s="3">
+      <c r="N47" s="3">
         <v>397900</v>
       </c>
-      <c r="M47" s="3">
+      <c r="O47" s="3">
         <v>381000</v>
       </c>
-      <c r="N47" s="3">
+      <c r="P47" s="3">
         <v>407500</v>
       </c>
-      <c r="O47" s="3">
+      <c r="Q47" s="3">
         <v>405600</v>
       </c>
-      <c r="P47" s="3">
+      <c r="R47" s="3">
         <v>555200</v>
       </c>
-      <c r="Q47" s="3">
+      <c r="S47" s="3">
         <v>509400</v>
       </c>
     </row>
-    <row r="48" spans="2:17" x14ac:dyDescent="0.2">
+    <row r="48" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C48" s="1" t="s">
         <v>41</v>
       </c>
       <c r="D48" s="3">
+        <v>984000</v>
+      </c>
+      <c r="E48" s="3">
+        <v>993100</v>
+      </c>
+      <c r="F48" s="3">
         <v>899400</v>
       </c>
-      <c r="E48" s="3">
+      <c r="G48" s="3">
         <v>898700</v>
       </c>
-      <c r="F48" s="3">
+      <c r="H48" s="3">
         <v>878600</v>
       </c>
-      <c r="G48" s="3">
+      <c r="I48" s="3">
         <v>808600</v>
       </c>
-      <c r="H48" s="3">
+      <c r="J48" s="3">
         <v>735700</v>
       </c>
-      <c r="I48" s="3">
+      <c r="K48" s="3">
         <v>792500</v>
       </c>
-      <c r="J48" s="3">
+      <c r="L48" s="3">
         <v>808100</v>
       </c>
-      <c r="K48" s="3">
+      <c r="M48" s="3">
         <v>813700</v>
       </c>
-      <c r="L48" s="3">
+      <c r="N48" s="3">
         <v>776500</v>
       </c>
-      <c r="M48" s="3">
+      <c r="O48" s="3">
         <v>743500</v>
       </c>
-      <c r="N48" s="3">
+      <c r="P48" s="3">
         <v>827100</v>
       </c>
-      <c r="O48" s="3">
+      <c r="Q48" s="3">
         <v>823100</v>
       </c>
-      <c r="P48" s="3">
+      <c r="R48" s="3">
         <v>819800</v>
       </c>
-      <c r="Q48" s="3">
+      <c r="S48" s="3">
         <v>752200</v>
       </c>
     </row>
-    <row r="49" spans="3:17" x14ac:dyDescent="0.2">
+    <row r="49" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C49" s="1" t="s">
         <v>42</v>
       </c>
       <c r="D49" s="3">
+        <v>5712700</v>
+      </c>
+      <c r="E49" s="3">
+        <v>5765400</v>
+      </c>
+      <c r="F49" s="3">
         <v>6070300</v>
       </c>
-      <c r="E49" s="3">
+      <c r="G49" s="3">
         <v>6066100</v>
       </c>
-      <c r="F49" s="3">
+      <c r="H49" s="3">
         <v>6712500</v>
       </c>
-      <c r="G49" s="3">
+      <c r="I49" s="3">
         <v>6177800</v>
       </c>
-      <c r="H49" s="3">
+      <c r="J49" s="3">
         <v>6207100</v>
       </c>
-      <c r="I49" s="3">
+      <c r="K49" s="3">
         <v>6686800</v>
       </c>
-      <c r="J49" s="3">
+      <c r="L49" s="3">
         <v>6723700</v>
       </c>
-      <c r="K49" s="3">
+      <c r="M49" s="3">
         <v>6770100</v>
       </c>
-      <c r="L49" s="3">
+      <c r="N49" s="3">
         <v>7135700</v>
       </c>
-      <c r="M49" s="3">
+      <c r="O49" s="3">
         <v>6832900</v>
       </c>
-      <c r="N49" s="3">
+      <c r="P49" s="3">
         <v>8144100</v>
       </c>
-      <c r="O49" s="3">
+      <c r="Q49" s="3">
         <v>8105200</v>
       </c>
-      <c r="P49" s="3">
+      <c r="R49" s="3">
         <v>8426600</v>
       </c>
-      <c r="Q49" s="3">
+      <c r="S49" s="3">
         <v>7731700</v>
       </c>
     </row>
-    <row r="50" spans="3:17" x14ac:dyDescent="0.2">
+    <row r="50" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C50" s="1" t="s">
         <v>43</v>
       </c>
@@ -2515,8 +2741,14 @@
       <c r="Q50" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="51" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R50" s="3">
+        <v>0</v>
+      </c>
+      <c r="S50" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="51" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C51" s="1" t="s">
         <v>44</v>
       </c>
@@ -2562,55 +2794,67 @@
       <c r="Q51" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="52" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R51" s="3">
+        <v>0</v>
+      </c>
+      <c r="S51" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="52" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C52" s="1" t="s">
         <v>45</v>
       </c>
       <c r="D52" s="3">
+        <v>1112500</v>
+      </c>
+      <c r="E52" s="3">
+        <v>1122800</v>
+      </c>
+      <c r="F52" s="3">
         <v>789400</v>
       </c>
-      <c r="E52" s="3">
+      <c r="G52" s="3">
         <v>788800</v>
       </c>
-      <c r="F52" s="3">
+      <c r="H52" s="3">
         <v>386300</v>
       </c>
-      <c r="G52" s="3">
+      <c r="I52" s="3">
         <v>355500</v>
       </c>
-      <c r="H52" s="3">
+      <c r="J52" s="3">
         <v>204400</v>
       </c>
-      <c r="I52" s="3">
+      <c r="K52" s="3">
         <v>220200</v>
       </c>
-      <c r="J52" s="3">
+      <c r="L52" s="3">
         <v>47700</v>
       </c>
-      <c r="K52" s="3">
+      <c r="M52" s="3">
         <v>48000</v>
       </c>
-      <c r="L52" s="3">
+      <c r="N52" s="3">
         <v>97600</v>
       </c>
-      <c r="M52" s="3">
+      <c r="O52" s="3">
         <v>93500</v>
       </c>
-      <c r="N52" s="3">
+      <c r="P52" s="3">
         <v>100200</v>
       </c>
-      <c r="O52" s="3">
+      <c r="Q52" s="3">
         <v>99700</v>
       </c>
-      <c r="P52" s="3">
+      <c r="R52" s="3">
         <v>163800</v>
       </c>
-      <c r="Q52" s="3">
+      <c r="S52" s="3">
         <v>150300</v>
       </c>
     </row>
-    <row r="53" spans="3:17" x14ac:dyDescent="0.2">
+    <row r="53" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C53" s="1" t="s">
         <v>46</v>
       </c>
@@ -2656,55 +2900,67 @@
       <c r="Q53" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="54" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R53" s="3">
+        <v>0</v>
+      </c>
+      <c r="S53" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="54" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C54" s="1" t="s">
         <v>47</v>
       </c>
       <c r="D54" s="3">
+        <v>12494500</v>
+      </c>
+      <c r="E54" s="3">
+        <v>12609700</v>
+      </c>
+      <c r="F54" s="3">
         <v>11987800</v>
       </c>
-      <c r="E54" s="3">
+      <c r="G54" s="3">
         <v>11979300</v>
       </c>
-      <c r="F54" s="3">
+      <c r="H54" s="3">
         <v>12875300</v>
       </c>
-      <c r="G54" s="3">
+      <c r="I54" s="3">
         <v>11849700</v>
       </c>
-      <c r="H54" s="3">
+      <c r="J54" s="3">
         <v>12858900</v>
       </c>
-      <c r="I54" s="3">
+      <c r="K54" s="3">
         <v>13852800</v>
       </c>
-      <c r="J54" s="3">
+      <c r="L54" s="3">
         <v>11141000</v>
       </c>
-      <c r="K54" s="3">
+      <c r="M54" s="3">
         <v>11217900</v>
       </c>
-      <c r="L54" s="3">
+      <c r="N54" s="3">
         <v>11592600</v>
       </c>
-      <c r="M54" s="3">
+      <c r="O54" s="3">
         <v>11100600</v>
       </c>
-      <c r="N54" s="3">
+      <c r="P54" s="3">
         <v>12756000</v>
       </c>
-      <c r="O54" s="3">
+      <c r="Q54" s="3">
         <v>12695000</v>
       </c>
-      <c r="P54" s="3">
+      <c r="R54" s="3">
         <v>13743900</v>
       </c>
-      <c r="Q54" s="3">
+      <c r="S54" s="3">
         <v>12610500</v>
       </c>
     </row>
-    <row r="55" spans="3:17" x14ac:dyDescent="0.2">
+    <row r="55" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C55" s="1" t="s">
         <v>48</v>
       </c>
@@ -2722,8 +2978,10 @@
       <c r="O55" s="3"/>
       <c r="P55" s="3"/>
       <c r="Q55" s="3"/>
-    </row>
-    <row r="56" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R55" s="3"/>
+      <c r="S55" s="3"/>
+    </row>
+    <row r="56" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C56" s="1" t="s">
         <v>49</v>
       </c>
@@ -2741,290 +2999,328 @@
       <c r="O56" s="3"/>
       <c r="P56" s="3"/>
       <c r="Q56" s="3"/>
-    </row>
-    <row r="57" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R56" s="3"/>
+      <c r="S56" s="3"/>
+    </row>
+    <row r="57" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C57" s="1" t="s">
         <v>50</v>
       </c>
       <c r="D57" s="3">
+        <v>676900</v>
+      </c>
+      <c r="E57" s="3">
+        <v>683200</v>
+      </c>
+      <c r="F57" s="3">
         <v>563500</v>
       </c>
-      <c r="E57" s="3">
+      <c r="G57" s="3">
         <v>563100</v>
       </c>
-      <c r="F57" s="3">
+      <c r="H57" s="3">
         <v>475900</v>
       </c>
-      <c r="G57" s="3">
+      <c r="I57" s="3">
         <v>438000</v>
       </c>
-      <c r="H57" s="3">
+      <c r="J57" s="3">
         <v>463100</v>
       </c>
-      <c r="I57" s="3">
+      <c r="K57" s="3">
         <v>498900</v>
       </c>
-      <c r="J57" s="3">
+      <c r="L57" s="3">
         <v>412000</v>
       </c>
-      <c r="K57" s="3">
+      <c r="M57" s="3">
         <v>414800</v>
       </c>
-      <c r="L57" s="3">
+      <c r="N57" s="3">
         <v>324600</v>
       </c>
-      <c r="M57" s="3">
+      <c r="O57" s="3">
         <v>310900</v>
       </c>
-      <c r="N57" s="3">
+      <c r="P57" s="3">
         <v>307000</v>
       </c>
-      <c r="O57" s="3">
+      <c r="Q57" s="3">
         <v>305500</v>
       </c>
-      <c r="P57" s="3">
+      <c r="R57" s="3">
         <v>342600</v>
       </c>
-      <c r="Q57" s="3">
+      <c r="S57" s="3">
         <v>314400</v>
       </c>
     </row>
-    <row r="58" spans="3:17" x14ac:dyDescent="0.2">
+    <row r="58" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C58" s="1" t="s">
         <v>51</v>
       </c>
       <c r="D58" s="3">
+        <v>192300</v>
+      </c>
+      <c r="E58" s="3">
+        <v>194100</v>
+      </c>
+      <c r="F58" s="3">
         <v>337800</v>
       </c>
-      <c r="E58" s="3">
+      <c r="G58" s="3">
         <v>337600</v>
       </c>
-      <c r="F58" s="3">
+      <c r="H58" s="3">
         <v>361000</v>
       </c>
-      <c r="G58" s="3">
+      <c r="I58" s="3">
         <v>332300</v>
       </c>
-      <c r="H58" s="3">
+      <c r="J58" s="3">
         <v>277300</v>
       </c>
-      <c r="I58" s="3">
+      <c r="K58" s="3">
         <v>298700</v>
       </c>
-      <c r="J58" s="3">
+      <c r="L58" s="3">
         <v>133400</v>
       </c>
-      <c r="K58" s="3">
+      <c r="M58" s="3">
         <v>134300</v>
       </c>
-      <c r="L58" s="3">
+      <c r="N58" s="3">
         <v>448500</v>
       </c>
-      <c r="M58" s="3">
+      <c r="O58" s="3">
         <v>429500</v>
       </c>
-      <c r="N58" s="3">
+      <c r="P58" s="3">
         <v>449200</v>
       </c>
-      <c r="O58" s="3">
+      <c r="Q58" s="3">
         <v>447100</v>
       </c>
-      <c r="P58" s="3">
+      <c r="R58" s="3">
         <v>136700</v>
       </c>
-      <c r="Q58" s="3">
+      <c r="S58" s="3">
         <v>125400</v>
       </c>
     </row>
-    <row r="59" spans="3:17" x14ac:dyDescent="0.2">
+    <row r="59" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C59" s="1" t="s">
         <v>52</v>
       </c>
       <c r="D59" s="3">
+        <v>3402500</v>
+      </c>
+      <c r="E59" s="3">
+        <v>3433900</v>
+      </c>
+      <c r="F59" s="3">
         <v>2566300</v>
       </c>
-      <c r="E59" s="3">
+      <c r="G59" s="3">
         <v>2564500</v>
       </c>
-      <c r="F59" s="3">
+      <c r="H59" s="3">
         <v>3441900</v>
       </c>
-      <c r="G59" s="3">
+      <c r="I59" s="3">
         <v>3167700</v>
       </c>
-      <c r="H59" s="3">
+      <c r="J59" s="3">
         <v>2715800</v>
       </c>
-      <c r="I59" s="3">
+      <c r="K59" s="3">
         <v>2925700</v>
       </c>
-      <c r="J59" s="3">
+      <c r="L59" s="3">
         <v>2416100</v>
       </c>
-      <c r="K59" s="3">
+      <c r="M59" s="3">
         <v>2432700</v>
       </c>
-      <c r="L59" s="3">
+      <c r="N59" s="3">
         <v>2057100</v>
       </c>
-      <c r="M59" s="3">
+      <c r="O59" s="3">
         <v>1969800</v>
       </c>
-      <c r="N59" s="3">
+      <c r="P59" s="3">
         <v>2126400</v>
       </c>
-      <c r="O59" s="3">
+      <c r="Q59" s="3">
         <v>2116300</v>
       </c>
-      <c r="P59" s="3">
+      <c r="R59" s="3">
         <v>1678600</v>
       </c>
-      <c r="Q59" s="3">
+      <c r="S59" s="3">
         <v>1540200</v>
       </c>
     </row>
-    <row r="60" spans="3:17" x14ac:dyDescent="0.2">
+    <row r="60" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C60" s="1" t="s">
         <v>53</v>
       </c>
       <c r="D60" s="3">
+        <v>4332000</v>
+      </c>
+      <c r="E60" s="3">
+        <v>4372000</v>
+      </c>
+      <c r="F60" s="3">
         <v>4023200</v>
       </c>
-      <c r="E60" s="3">
+      <c r="G60" s="3">
         <v>4020400</v>
       </c>
-      <c r="F60" s="3">
+      <c r="H60" s="3">
         <v>4328100</v>
       </c>
-      <c r="G60" s="3">
+      <c r="I60" s="3">
         <v>3983400</v>
       </c>
-      <c r="H60" s="3">
+      <c r="J60" s="3">
         <v>3864500</v>
       </c>
-      <c r="I60" s="3">
+      <c r="K60" s="3">
         <v>4163200</v>
       </c>
-      <c r="J60" s="3">
+      <c r="L60" s="3">
         <v>3012600</v>
       </c>
-      <c r="K60" s="3">
+      <c r="M60" s="3">
         <v>3033400</v>
       </c>
-      <c r="L60" s="3">
+      <c r="N60" s="3">
         <v>3254600</v>
       </c>
-      <c r="M60" s="3">
+      <c r="O60" s="3">
         <v>3116400</v>
       </c>
-      <c r="N60" s="3">
+      <c r="P60" s="3">
         <v>2935300</v>
       </c>
-      <c r="O60" s="3">
+      <c r="Q60" s="3">
         <v>2921200</v>
       </c>
-      <c r="P60" s="3">
+      <c r="R60" s="3">
         <v>2567400</v>
       </c>
-      <c r="Q60" s="3">
+      <c r="S60" s="3">
         <v>2355700</v>
       </c>
     </row>
-    <row r="61" spans="3:17" x14ac:dyDescent="0.2">
+    <row r="61" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C61" s="1" t="s">
         <v>54</v>
       </c>
       <c r="D61" s="3">
+        <v>5875400</v>
+      </c>
+      <c r="E61" s="3">
+        <v>5929600</v>
+      </c>
+      <c r="F61" s="3">
         <v>5093100</v>
       </c>
-      <c r="E61" s="3">
+      <c r="G61" s="3">
         <v>5089500</v>
       </c>
-      <c r="F61" s="3">
+      <c r="H61" s="3">
         <v>5083100</v>
       </c>
-      <c r="G61" s="3">
+      <c r="I61" s="3">
         <v>4678200</v>
       </c>
-      <c r="H61" s="3">
+      <c r="J61" s="3">
         <v>5590200</v>
       </c>
-      <c r="I61" s="3">
+      <c r="K61" s="3">
         <v>6022300</v>
       </c>
-      <c r="J61" s="3">
+      <c r="L61" s="3">
         <v>5859500</v>
       </c>
-      <c r="K61" s="3">
+      <c r="M61" s="3">
         <v>5900000</v>
       </c>
-      <c r="L61" s="3">
+      <c r="N61" s="3">
         <v>5788700</v>
       </c>
-      <c r="M61" s="3">
+      <c r="O61" s="3">
         <v>5543000</v>
       </c>
-      <c r="N61" s="3">
+      <c r="P61" s="3">
         <v>5662000</v>
       </c>
-      <c r="O61" s="3">
+      <c r="Q61" s="3">
         <v>5634900</v>
       </c>
-      <c r="P61" s="3">
+      <c r="R61" s="3">
         <v>5938500</v>
       </c>
-      <c r="Q61" s="3">
+      <c r="S61" s="3">
         <v>5448800</v>
       </c>
     </row>
-    <row r="62" spans="3:17" x14ac:dyDescent="0.2">
+    <row r="62" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C62" s="1" t="s">
         <v>55</v>
       </c>
       <c r="D62" s="3">
+        <v>511600</v>
+      </c>
+      <c r="E62" s="3">
+        <v>516300</v>
+      </c>
+      <c r="F62" s="3">
         <v>533900</v>
       </c>
-      <c r="E62" s="3">
+      <c r="G62" s="3">
         <v>533500</v>
       </c>
-      <c r="F62" s="3">
+      <c r="H62" s="3">
         <v>465500</v>
       </c>
-      <c r="G62" s="3">
+      <c r="I62" s="3">
         <v>428400</v>
       </c>
-      <c r="H62" s="3">
+      <c r="J62" s="3">
         <v>323300</v>
       </c>
-      <c r="I62" s="3">
+      <c r="K62" s="3">
         <v>348300</v>
       </c>
-      <c r="J62" s="3">
+      <c r="L62" s="3">
         <v>665800</v>
       </c>
-      <c r="K62" s="3">
+      <c r="M62" s="3">
         <v>670400</v>
       </c>
-      <c r="L62" s="3">
+      <c r="N62" s="3">
         <v>413100</v>
       </c>
-      <c r="M62" s="3">
+      <c r="O62" s="3">
         <v>395500</v>
       </c>
-      <c r="N62" s="3">
+      <c r="P62" s="3">
         <v>508500</v>
       </c>
-      <c r="O62" s="3">
+      <c r="Q62" s="3">
         <v>506100</v>
       </c>
-      <c r="P62" s="3">
+      <c r="R62" s="3">
         <v>874400</v>
       </c>
-      <c r="Q62" s="3">
+      <c r="S62" s="3">
         <v>802300</v>
       </c>
     </row>
-    <row r="63" spans="3:17" x14ac:dyDescent="0.2">
+    <row r="63" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C63" s="1" t="s">
         <v>56</v>
       </c>
@@ -3070,8 +3366,14 @@
       <c r="Q63" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="64" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R63" s="3">
+        <v>0</v>
+      </c>
+      <c r="S63" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="64" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C64" s="1" t="s">
         <v>20</v>
       </c>
@@ -3117,8 +3419,14 @@
       <c r="Q64" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="65" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="R64" s="3">
+        <v>0</v>
+      </c>
+      <c r="S64" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="65" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C65" s="1" t="s">
         <v>57</v>
       </c>
@@ -3164,55 +3472,67 @@
       <c r="Q65" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="66" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="R65" s="3">
+        <v>0</v>
+      </c>
+      <c r="S65" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="66" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C66" s="1" t="s">
         <v>58</v>
       </c>
       <c r="D66" s="3">
+        <v>10928900</v>
+      </c>
+      <c r="E66" s="3">
+        <v>11029700</v>
+      </c>
+      <c r="F66" s="3">
         <v>9881600</v>
       </c>
-      <c r="E66" s="3">
+      <c r="G66" s="3">
         <v>9874700</v>
       </c>
-      <c r="F66" s="3">
+      <c r="H66" s="3">
         <v>10131300</v>
       </c>
-      <c r="G66" s="3">
+      <c r="I66" s="3">
         <v>9324300</v>
       </c>
-      <c r="H66" s="3">
+      <c r="J66" s="3">
         <v>10050600</v>
       </c>
-      <c r="I66" s="3">
+      <c r="K66" s="3">
         <v>10827500</v>
       </c>
-      <c r="J66" s="3">
+      <c r="L66" s="3">
         <v>9807100</v>
       </c>
-      <c r="K66" s="3">
+      <c r="M66" s="3">
         <v>9874900</v>
       </c>
-      <c r="L66" s="3">
+      <c r="N66" s="3">
         <v>9769400</v>
       </c>
-      <c r="M66" s="3">
+      <c r="O66" s="3">
         <v>9354800</v>
       </c>
-      <c r="N66" s="3">
+      <c r="P66" s="3">
         <v>9442500</v>
       </c>
-      <c r="O66" s="3">
+      <c r="Q66" s="3">
         <v>9397300</v>
       </c>
-      <c r="P66" s="3">
+      <c r="R66" s="3">
         <v>9710900</v>
       </c>
-      <c r="Q66" s="3">
+      <c r="S66" s="3">
         <v>8910100</v>
       </c>
     </row>
-    <row r="67" spans="2:17" x14ac:dyDescent="0.2">
+    <row r="67" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C67" s="1" t="s">
         <v>59</v>
       </c>
@@ -3230,8 +3550,10 @@
       <c r="O67" s="3"/>
       <c r="P67" s="3"/>
       <c r="Q67" s="3"/>
-    </row>
-    <row r="68" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="R67" s="3"/>
+      <c r="S67" s="3"/>
+    </row>
+    <row r="68" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C68" s="1" t="s">
         <v>60</v>
       </c>
@@ -3277,8 +3599,14 @@
       <c r="Q68" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="69" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="R68" s="3">
+        <v>0</v>
+      </c>
+      <c r="S68" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="69" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C69" s="1" t="s">
         <v>61</v>
       </c>
@@ -3324,8 +3652,14 @@
       <c r="Q69" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="70" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="R69" s="3">
+        <v>0</v>
+      </c>
+      <c r="S69" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="70" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C70" s="1" t="s">
         <v>62</v>
       </c>
@@ -3371,8 +3705,14 @@
       <c r="Q70" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="71" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="R70" s="3">
+        <v>0</v>
+      </c>
+      <c r="S70" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="71" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C71" s="1" t="s">
         <v>63</v>
       </c>
@@ -3418,55 +3758,67 @@
       <c r="Q71" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="72" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="R71" s="3">
+        <v>0</v>
+      </c>
+      <c r="S71" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="72" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C72" s="1" t="s">
         <v>64</v>
       </c>
       <c r="D72" s="3">
+        <v>-13196700</v>
+      </c>
+      <c r="E72" s="3">
+        <v>-13318500</v>
+      </c>
+      <c r="F72" s="3">
         <v>-12985000</v>
       </c>
-      <c r="E72" s="3">
+      <c r="G72" s="3">
         <v>-12975800</v>
       </c>
-      <c r="F72" s="3">
+      <c r="H72" s="3">
         <v>-12448700</v>
       </c>
-      <c r="G72" s="3">
+      <c r="I72" s="3">
         <v>-11457100</v>
       </c>
-      <c r="H72" s="3">
+      <c r="J72" s="3">
         <v>-10433900</v>
       </c>
-      <c r="I72" s="3">
+      <c r="K72" s="3">
         <v>-11240400</v>
       </c>
-      <c r="J72" s="3">
+      <c r="L72" s="3">
         <v>-10401100</v>
       </c>
-      <c r="K72" s="3">
+      <c r="M72" s="3">
         <v>-10472900</v>
       </c>
-      <c r="L72" s="3">
+      <c r="N72" s="3">
         <v>-9739100</v>
       </c>
-      <c r="M72" s="3">
+      <c r="O72" s="3">
         <v>-9325800</v>
       </c>
-      <c r="N72" s="3">
+      <c r="P72" s="3">
         <v>-7930300</v>
       </c>
-      <c r="O72" s="3">
+      <c r="Q72" s="3">
         <v>-7892400</v>
       </c>
-      <c r="P72" s="3">
+      <c r="R72" s="3">
         <v>-6833800</v>
       </c>
-      <c r="Q72" s="3">
+      <c r="S72" s="3">
         <v>-6270200</v>
       </c>
     </row>
-    <row r="73" spans="2:17" x14ac:dyDescent="0.2">
+    <row r="73" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C73" s="1" t="s">
         <v>65</v>
       </c>
@@ -3512,8 +3864,14 @@
       <c r="Q73" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="74" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="R73" s="3">
+        <v>0</v>
+      </c>
+      <c r="S73" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="74" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C74" s="1" t="s">
         <v>66</v>
       </c>
@@ -3559,8 +3917,14 @@
       <c r="Q74" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="75" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="R74" s="3">
+        <v>0</v>
+      </c>
+      <c r="S74" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="75" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C75" s="1" t="s">
         <v>67</v>
       </c>
@@ -3606,55 +3970,67 @@
       <c r="Q75" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="76" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="R75" s="3">
+        <v>0</v>
+      </c>
+      <c r="S75" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="76" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C76" s="1" t="s">
         <v>68</v>
       </c>
       <c r="D76" s="3">
+        <v>1396700</v>
+      </c>
+      <c r="E76" s="3">
+        <v>1409500</v>
+      </c>
+      <c r="F76" s="3">
         <v>1925100</v>
       </c>
-      <c r="E76" s="3">
+      <c r="G76" s="3">
         <v>1923700</v>
       </c>
-      <c r="F76" s="3">
+      <c r="H76" s="3">
         <v>2578300</v>
       </c>
-      <c r="G76" s="3">
+      <c r="I76" s="3">
         <v>2372900</v>
       </c>
-      <c r="H76" s="3">
+      <c r="J76" s="3">
         <v>2683800</v>
       </c>
-      <c r="I76" s="3">
+      <c r="K76" s="3">
         <v>2891300</v>
       </c>
-      <c r="J76" s="3">
+      <c r="L76" s="3">
         <v>1340300</v>
       </c>
-      <c r="K76" s="3">
+      <c r="M76" s="3">
         <v>1349600</v>
       </c>
-      <c r="L76" s="3">
+      <c r="N76" s="3">
         <v>1827700</v>
       </c>
-      <c r="M76" s="3">
+      <c r="O76" s="3">
         <v>1750100</v>
       </c>
-      <c r="N76" s="3">
+      <c r="P76" s="3">
         <v>3316800</v>
       </c>
-      <c r="O76" s="3">
+      <c r="Q76" s="3">
         <v>3301000</v>
       </c>
-      <c r="P76" s="3">
+      <c r="R76" s="3">
         <v>3975300</v>
       </c>
-      <c r="Q76" s="3">
+      <c r="S76" s="3">
         <v>3647500</v>
       </c>
     </row>
-    <row r="77" spans="2:17" x14ac:dyDescent="0.2">
+    <row r="77" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C77" s="1" t="s">
         <v>69</v>
       </c>
@@ -3700,60 +4076,72 @@
       <c r="Q77" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="79" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="R77" s="3">
+        <v>0</v>
+      </c>
+      <c r="S77" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="79" spans="2:19" x14ac:dyDescent="0.2">
       <c r="B79" s="1" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="80" spans="2:17" x14ac:dyDescent="0.2">
+    <row r="80" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C80" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D80" s="2">
+        <v>46203</v>
+      </c>
+      <c r="E80" s="2">
+        <v>46112</v>
+      </c>
+      <c r="F80" s="2">
         <v>46022</v>
       </c>
-      <c r="E80" s="2">
+      <c r="G80" s="2">
         <v>45930</v>
       </c>
-      <c r="F80" s="2">
+      <c r="H80" s="2">
         <v>45838</v>
       </c>
-      <c r="G80" s="2">
+      <c r="I80" s="2">
         <v>45747</v>
       </c>
-      <c r="H80" s="2">
+      <c r="J80" s="2">
         <v>45657</v>
       </c>
-      <c r="I80" s="2">
+      <c r="K80" s="2">
         <v>45565</v>
       </c>
-      <c r="J80" s="2">
+      <c r="L80" s="2">
         <v>45473</v>
       </c>
-      <c r="K80" s="2">
+      <c r="M80" s="2">
         <v>45382</v>
       </c>
-      <c r="L80" s="2">
+      <c r="N80" s="2">
         <v>45291</v>
       </c>
-      <c r="M80" s="2">
+      <c r="O80" s="2">
         <v>45199</v>
       </c>
-      <c r="N80" s="2">
+      <c r="P80" s="2">
         <v>45107</v>
       </c>
-      <c r="O80" s="2">
+      <c r="Q80" s="2">
         <v>45016</v>
       </c>
-      <c r="P80" s="2">
+      <c r="R80" s="2">
         <v>44926</v>
       </c>
-      <c r="Q80" s="2">
+      <c r="S80" s="2">
         <v>44834</v>
       </c>
     </row>
-    <row r="81" spans="3:17" x14ac:dyDescent="0.2">
+    <row r="81" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C81" s="1" t="s">
         <v>28</v>
       </c>
@@ -3799,8 +4187,14 @@
       <c r="Q81" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="82" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R81" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="S81" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="82" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C82" s="1" t="s">
         <v>71</v>
       </c>
@@ -3818,55 +4212,63 @@
       <c r="O82" s="3"/>
       <c r="P82" s="3"/>
       <c r="Q82" s="3"/>
-    </row>
-    <row r="83" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R82" s="3"/>
+      <c r="S82" s="3"/>
+    </row>
+    <row r="83" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C83" s="1" t="s">
         <v>72</v>
       </c>
       <c r="D83" s="3">
+        <v>101900</v>
+      </c>
+      <c r="E83" s="3">
+        <v>93800</v>
+      </c>
+      <c r="F83" s="3">
         <v>45400</v>
       </c>
-      <c r="E83" s="3">
+      <c r="G83" s="3">
         <v>49000</v>
       </c>
-      <c r="F83" s="3">
+      <c r="H83" s="3">
         <v>87800</v>
       </c>
-      <c r="G83" s="3">
+      <c r="I83" s="3">
         <v>88400</v>
       </c>
-      <c r="H83" s="3">
+      <c r="J83" s="3">
         <v>30000</v>
       </c>
-      <c r="I83" s="3">
+      <c r="K83" s="3">
         <v>28700</v>
       </c>
-      <c r="J83" s="3">
+      <c r="L83" s="3">
         <v>99800</v>
       </c>
-      <c r="K83" s="3">
+      <c r="M83" s="3">
         <v>99300</v>
       </c>
-      <c r="L83" s="3">
+      <c r="N83" s="3">
         <v>71000</v>
       </c>
-      <c r="M83" s="3">
+      <c r="O83" s="3">
         <v>65200</v>
       </c>
-      <c r="N83" s="3">
+      <c r="P83" s="3">
         <v>84700</v>
       </c>
-      <c r="O83" s="3">
+      <c r="Q83" s="3">
         <v>90000</v>
       </c>
-      <c r="P83" s="3">
+      <c r="R83" s="3">
         <v>57900</v>
       </c>
-      <c r="Q83" s="3">
+      <c r="S83" s="3">
         <v>59000</v>
       </c>
     </row>
-    <row r="84" spans="3:17" x14ac:dyDescent="0.2">
+    <row r="84" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C84" s="1" t="s">
         <v>73</v>
       </c>
@@ -3912,8 +4314,14 @@
       <c r="Q84" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="85" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R84" s="3">
+        <v>0</v>
+      </c>
+      <c r="S84" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="85" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C85" s="1" t="s">
         <v>74</v>
       </c>
@@ -3959,8 +4367,14 @@
       <c r="Q85" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="86" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R85" s="3">
+        <v>0</v>
+      </c>
+      <c r="S85" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="86" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C86" s="1" t="s">
         <v>75</v>
       </c>
@@ -4006,8 +4420,14 @@
       <c r="Q86" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="87" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R86" s="3">
+        <v>0</v>
+      </c>
+      <c r="S86" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="87" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C87" s="1" t="s">
         <v>76</v>
       </c>
@@ -4053,8 +4473,14 @@
       <c r="Q87" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="88" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R87" s="3">
+        <v>0</v>
+      </c>
+      <c r="S87" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="88" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C88" s="1" t="s">
         <v>77</v>
       </c>
@@ -4100,55 +4526,67 @@
       <c r="Q88" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="89" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R88" s="3">
+        <v>0</v>
+      </c>
+      <c r="S88" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="89" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C89" s="1" t="s">
         <v>78</v>
       </c>
       <c r="D89" s="3">
+        <v>305500</v>
+      </c>
+      <c r="E89" s="3">
+        <v>308300</v>
+      </c>
+      <c r="F89" s="3">
         <v>-185500</v>
       </c>
-      <c r="E89" s="3">
+      <c r="G89" s="3">
         <v>-185300</v>
       </c>
-      <c r="F89" s="3">
+      <c r="H89" s="3">
         <v>232200</v>
       </c>
-      <c r="G89" s="3">
+      <c r="I89" s="3">
         <v>213700</v>
       </c>
-      <c r="H89" s="3">
+      <c r="J89" s="3">
         <v>277000</v>
       </c>
-      <c r="I89" s="3">
+      <c r="K89" s="3">
         <v>298400</v>
       </c>
-      <c r="J89" s="3">
+      <c r="L89" s="3">
         <v>55300</v>
       </c>
-      <c r="K89" s="3">
+      <c r="M89" s="3">
         <v>55700</v>
       </c>
-      <c r="L89" s="3">
+      <c r="N89" s="3">
         <v>87200</v>
       </c>
-      <c r="M89" s="3">
+      <c r="O89" s="3">
         <v>83500</v>
       </c>
-      <c r="N89" s="3">
+      <c r="P89" s="3">
         <v>-96700</v>
       </c>
-      <c r="O89" s="3">
+      <c r="Q89" s="3">
         <v>-96300</v>
       </c>
-      <c r="P89" s="3">
+      <c r="R89" s="3">
         <v>-153300</v>
       </c>
-      <c r="Q89" s="3">
+      <c r="S89" s="3">
         <v>-140700</v>
       </c>
     </row>
-    <row r="90" spans="3:17" x14ac:dyDescent="0.2">
+    <row r="90" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C90" s="1" t="s">
         <v>79</v>
       </c>
@@ -4166,55 +4604,63 @@
       <c r="O90" s="3"/>
       <c r="P90" s="3"/>
       <c r="Q90" s="3"/>
-    </row>
-    <row r="91" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R90" s="3"/>
+      <c r="S90" s="3"/>
+    </row>
+    <row r="91" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C91" s="1" t="s">
         <v>80</v>
       </c>
       <c r="D91" s="3">
+        <v>-31500</v>
+      </c>
+      <c r="E91" s="3">
+        <v>-31800</v>
+      </c>
+      <c r="F91" s="3">
         <v>-53700</v>
       </c>
-      <c r="E91" s="3">
+      <c r="G91" s="3">
         <v>-53600</v>
       </c>
-      <c r="F91" s="3">
+      <c r="H91" s="3">
         <v>-46700</v>
       </c>
-      <c r="G91" s="3">
+      <c r="I91" s="3">
         <v>-43000</v>
       </c>
-      <c r="H91" s="3">
+      <c r="J91" s="3">
         <v>-39300</v>
       </c>
-      <c r="I91" s="3">
+      <c r="K91" s="3">
         <v>-42400</v>
       </c>
-      <c r="J91" s="3">
+      <c r="L91" s="3">
         <v>-33800</v>
       </c>
-      <c r="K91" s="3">
+      <c r="M91" s="3">
         <v>-34000</v>
       </c>
-      <c r="L91" s="3">
+      <c r="N91" s="3">
         <v>-46900</v>
       </c>
-      <c r="M91" s="3">
+      <c r="O91" s="3">
         <v>-44900</v>
       </c>
-      <c r="N91" s="3">
+      <c r="P91" s="3">
         <v>-34300</v>
       </c>
-      <c r="O91" s="3">
+      <c r="Q91" s="3">
         <v>-34100</v>
       </c>
-      <c r="P91" s="3">
+      <c r="R91" s="3">
         <v>-42900</v>
       </c>
-      <c r="Q91" s="3">
+      <c r="S91" s="3">
         <v>-39400</v>
       </c>
     </row>
-    <row r="92" spans="3:17" x14ac:dyDescent="0.2">
+    <row r="92" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C92" s="1" t="s">
         <v>81</v>
       </c>
@@ -4260,8 +4706,14 @@
       <c r="Q92" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="93" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R92" s="3">
+        <v>0</v>
+      </c>
+      <c r="S92" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="93" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C93" s="1" t="s">
         <v>82</v>
       </c>
@@ -4307,55 +4759,67 @@
       <c r="Q93" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="94" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R93" s="3">
+        <v>0</v>
+      </c>
+      <c r="S93" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="94" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C94" s="1" t="s">
         <v>83</v>
       </c>
       <c r="D94" s="3">
+        <v>-62900</v>
+      </c>
+      <c r="E94" s="3">
+        <v>-63500</v>
+      </c>
+      <c r="F94" s="3">
         <v>-42000</v>
       </c>
-      <c r="E94" s="3">
+      <c r="G94" s="3">
         <v>-41900</v>
       </c>
-      <c r="F94" s="3">
+      <c r="H94" s="3">
         <v>-100600</v>
       </c>
-      <c r="G94" s="3">
+      <c r="I94" s="3">
         <v>-92600</v>
       </c>
-      <c r="H94" s="3">
+      <c r="J94" s="3">
         <v>-55500</v>
       </c>
-      <c r="I94" s="3">
+      <c r="K94" s="3">
         <v>-59800</v>
       </c>
-      <c r="J94" s="3">
+      <c r="L94" s="3">
         <v>25600</v>
       </c>
-      <c r="K94" s="3">
+      <c r="M94" s="3">
         <v>25700</v>
       </c>
-      <c r="L94" s="3">
+      <c r="N94" s="3">
         <v>-91400</v>
       </c>
-      <c r="M94" s="3">
+      <c r="O94" s="3">
         <v>-87500</v>
       </c>
-      <c r="N94" s="3">
+      <c r="P94" s="3">
         <v>-50400</v>
       </c>
-      <c r="O94" s="3">
+      <c r="Q94" s="3">
         <v>-50200</v>
       </c>
-      <c r="P94" s="3">
+      <c r="R94" s="3">
         <v>23100</v>
       </c>
-      <c r="Q94" s="3">
+      <c r="S94" s="3">
         <v>21200</v>
       </c>
     </row>
-    <row r="95" spans="3:17" x14ac:dyDescent="0.2">
+    <row r="95" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C95" s="1" t="s">
         <v>84</v>
       </c>
@@ -4373,8 +4837,10 @@
       <c r="O95" s="3"/>
       <c r="P95" s="3"/>
       <c r="Q95" s="3"/>
-    </row>
-    <row r="96" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R95" s="3"/>
+      <c r="S95" s="3"/>
+    </row>
+    <row r="96" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C96" s="1" t="s">
         <v>85</v>
       </c>
@@ -4420,8 +4886,14 @@
       <c r="Q96" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="97" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R96" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="S96" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="97" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C97" s="1" t="s">
         <v>86</v>
       </c>
@@ -4467,8 +4939,14 @@
       <c r="Q97" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="98" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R97" s="3">
+        <v>0</v>
+      </c>
+      <c r="S97" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="98" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C98" s="1" t="s">
         <v>87</v>
       </c>
@@ -4514,8 +4992,14 @@
       <c r="Q98" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="99" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R98" s="3">
+        <v>0</v>
+      </c>
+      <c r="S98" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="99" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C99" s="1" t="s">
         <v>88</v>
       </c>
@@ -4561,145 +5045,169 @@
       <c r="Q99" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="100" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R99" s="3">
+        <v>0</v>
+      </c>
+      <c r="S99" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="100" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C100" s="1" t="s">
         <v>89</v>
       </c>
       <c r="D100" s="3">
+        <v>133300</v>
+      </c>
+      <c r="E100" s="3">
+        <v>134500</v>
+      </c>
+      <c r="F100" s="3">
         <v>-167800</v>
       </c>
-      <c r="E100" s="3">
+      <c r="G100" s="3">
         <v>-167700</v>
       </c>
-      <c r="F100" s="3">
+      <c r="H100" s="3">
         <v>-640400</v>
       </c>
-      <c r="G100" s="3">
+      <c r="I100" s="3">
         <v>-589400</v>
       </c>
-      <c r="H100" s="3">
+      <c r="J100" s="3">
         <v>835500</v>
       </c>
-      <c r="I100" s="3">
+      <c r="K100" s="3">
         <v>900100</v>
       </c>
-      <c r="J100" s="3">
+      <c r="L100" s="3">
         <v>-18400</v>
       </c>
-      <c r="K100" s="3">
+      <c r="M100" s="3">
         <v>-18600</v>
       </c>
-      <c r="L100" s="3">
+      <c r="N100" s="3">
         <v>-128800</v>
       </c>
-      <c r="M100" s="3">
+      <c r="O100" s="3">
         <v>-123400</v>
       </c>
-      <c r="N100" s="3">
+      <c r="P100" s="3">
         <v>-78700</v>
       </c>
-      <c r="O100" s="3">
+      <c r="Q100" s="3">
         <v>-78300</v>
       </c>
-      <c r="P100" s="3">
+      <c r="R100" s="3">
         <v>-128500</v>
       </c>
-      <c r="Q100" s="3">
+      <c r="S100" s="3">
         <v>-117900</v>
       </c>
     </row>
-    <row r="101" spans="3:17" x14ac:dyDescent="0.2">
+    <row r="101" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C101" s="1" t="s">
         <v>90</v>
       </c>
       <c r="D101" s="3">
+        <v>-78700</v>
+      </c>
+      <c r="E101" s="3">
+        <v>-72400</v>
+      </c>
+      <c r="F101" s="3">
         <v>5600</v>
       </c>
-      <c r="E101" s="3">
+      <c r="G101" s="3">
         <v>6000</v>
       </c>
-      <c r="F101" s="3">
+      <c r="H101" s="3">
         <v>-10700</v>
       </c>
-      <c r="G101" s="3">
+      <c r="I101" s="3">
         <v>-10700</v>
       </c>
-      <c r="H101" s="3">
+      <c r="J101" s="3">
         <v>-13400</v>
       </c>
-      <c r="I101" s="3">
+      <c r="K101" s="3">
         <v>-12900</v>
       </c>
-      <c r="J101" s="3">
+      <c r="L101" s="3">
         <v>-43400</v>
       </c>
-      <c r="K101" s="3">
+      <c r="M101" s="3">
         <v>-43200</v>
       </c>
-      <c r="L101" s="3">
+      <c r="N101" s="3">
         <v>-19200</v>
       </c>
-      <c r="M101" s="3">
+      <c r="O101" s="3">
         <v>-17600</v>
       </c>
-      <c r="N101" s="3">
+      <c r="P101" s="3">
         <v>23300</v>
       </c>
-      <c r="O101" s="3">
+      <c r="Q101" s="3">
         <v>24700</v>
       </c>
-      <c r="P101" s="3">
+      <c r="R101" s="3">
         <v>3900</v>
       </c>
-      <c r="Q101" s="3">
+      <c r="S101" s="3">
         <v>4000</v>
       </c>
     </row>
-    <row r="102" spans="3:17" x14ac:dyDescent="0.2">
+    <row r="102" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C102" s="1" t="s">
         <v>91</v>
       </c>
       <c r="D102" s="3">
+        <v>376400</v>
+      </c>
+      <c r="E102" s="3">
+        <v>379900</v>
+      </c>
+      <c r="F102" s="3">
         <v>-408200</v>
       </c>
-      <c r="E102" s="3">
+      <c r="G102" s="3">
         <v>-408000</v>
       </c>
-      <c r="F102" s="3">
+      <c r="H102" s="3">
         <v>-587500</v>
       </c>
-      <c r="G102" s="3">
+      <c r="I102" s="3">
         <v>-540700</v>
       </c>
-      <c r="H102" s="3">
+      <c r="J102" s="3">
         <v>1062600</v>
       </c>
-      <c r="I102" s="3">
+      <c r="K102" s="3">
         <v>1144700</v>
       </c>
-      <c r="J102" s="3">
+      <c r="L102" s="3">
         <v>51800</v>
       </c>
-      <c r="K102" s="3">
+      <c r="M102" s="3">
         <v>52100</v>
       </c>
-      <c r="L102" s="3">
+      <c r="N102" s="3">
         <v>-146500</v>
       </c>
-      <c r="M102" s="3">
+      <c r="O102" s="3">
         <v>-140300</v>
       </c>
-      <c r="N102" s="3">
+      <c r="P102" s="3">
         <v>-269300</v>
       </c>
-      <c r="O102" s="3">
+      <c r="Q102" s="3">
         <v>-268000</v>
       </c>
-      <c r="P102" s="3">
+      <c r="R102" s="3">
         <v>-277900</v>
       </c>
-      <c r="Q102" s="3">
+      <c r="S102" s="3">
         <v>-255000</v>
       </c>
     </row>
